--- a/output/extracted_urls/autonews/autonews_urls.xlsx
+++ b/output/extracted_urls/autonews/autonews_urls.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -494,7 +494,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Body is just a newsletter/date plus a featured-story link, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a newsletter/date header and a featured-story link, with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Body is mostly a dated teaser/featured-story page with no engineering narrative or R&amp;D content.</t>
+          <t>Body is mostly a headline/date and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Body is just a sales-data/listing page with featured story links, not an engineering or R&amp;D article.</t>
+          <t>This is a sales/data-center page with featured story links, not an engineering-focused article body.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Body is just a sales-data listing with featured-story links, not an engineering or R&amp;D article.</t>
+          <t>Body is a featured-stories/listing page with sales snippets, not an engineering article.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -649,7 +649,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>This is a sales/incentives listing page with no substantive engineering or R&amp;D content in the body.</t>
+          <t>Body is just a sales-data landing page with featured story links and no engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -699,7 +699,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The body is mostly a featured-story teaser and dealership-listing blurb, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-stories teaser/listing with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories teaser with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story teaser and date block with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story/listing page with no substantive article narrative or engineering detail.</t>
+          <t>The body is mostly navigation and featured-story links, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -822,7 +822,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Body is mostly featured-story/navigation text with no substantive engineering narrative.</t>
+          <t>Body is mostly dates and featured-story navigation, with no substantive engineering article narrative.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Body is just a sponsored episode header with no engineering or technical article narrative.</t>
+          <t>Body is just a sponsored episode header/date with no engineering narrative or technical content.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -904,7 +904,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Body is just dates and featured-story/listing text with no engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-stories teaser and dealership-list blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Body is just a promotional white-paper heading with no engineering or R&amp;D substance.</t>
+          <t>Body is just a promo/header for a dealership AI white paper, with no substantive engineering or automotive R&amp;D content.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -986,7 +986,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Body is essentially a landing-page header with no substantive engineering article content.</t>
+          <t>Body is just a promo header with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Body is just a featured-story teaser and sales blurb, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-story teaser and date metadata, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story link and date metadata, with no substantive engineering narrative.</t>
+          <t>Body is just a featured-story blurb and a dealership list teaser, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a date stamp and featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Body is mostly date stamps and a featured-story teaser, with no substantive engineering narrative.</t>
+          <t>Body is mostly dateline and featured-story navigation with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories blurb with no substantive engineering article or technical detail.</t>
+          <t>Body is just a featured-stories teaser and dates, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1223,7 +1223,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Body is just a lawsuit headline and featured-story link with no engineering or technical article narrative.</t>
+          <t>Body is just a short dealership finance lawsuit teaser with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories teaser and date line, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is essentially a featured-story teaser and dealership list promo, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Body is mostly date/meta and a featured-story teaser, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly metadata and a featured-story teaser, with no substantive engineering or R&amp;D discussion.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -1346,7 +1346,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories blurb and article teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story blurb and metadata, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Body is mostly date metadata and a featured-story link, with no substantive article narrative about engineering or R&amp;D.</t>
+          <t>Body is just a featured-story blurb and unrelated dealership sales teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Body is essentially a featured-story blurb and list item, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story teaser and dealership ranking blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1469,7 +1469,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>The body is just a webcast form and registration prompts, with no substantive engineering article content.</t>
+          <t>Body is just a webcast registration form with no engineering article content.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>This is a webcast registration form with no substantive engineering article body.</t>
+          <t>Webinar signup page with form fields only, no substantive engineering article body.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Body is just a headline and teaser about dealership acquisitions, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a dealership acquisition headline and a teaser link, with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Body is mostly dates and a featured-story link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-story teaser and date metadata, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1633,7 +1633,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Body is just a webcast registration form with no article narrative or engineering content.</t>
+          <t>Body is just a webcast registration form with no engineering or article content.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -1674,7 +1674,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Body is just dates and a featured-story teaser with no substantive engineering article narrative.</t>
+          <t>Body is just a featured-story listing with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Body is mostly byline/date and featured story navigation, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a guest commentary header and featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>The body is just a newsletter header and a linked list item, with no substantive engineering discussion.</t>
+          <t>The body is just a newsletter header and a featured-story link, with no substantive engineering narrative about Ford’s EREV or Lightning lessons.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories blurb and sales/share teaser, with no engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story link and a sales blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Body is just a short personnel note with a featured-story link, not an engineering or R&amp;D article.</t>
+          <t>Body is just a brief executive-sales update with navigation/featured-story content, not engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-stories promo with no substantive engineering narrative, so it offers no R&amp;D value.</t>
+          <t>Body is mostly a featured-story/listing page with a dealership article teaser, not substantive engineering content.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering article content.</t>
+          <t>Body is mostly a featured-story teaser and date block with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Body is mostly featured-story/navigation text with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just date/featured-story metadata and a teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2035,7 +2035,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-link blurb and date with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a headline, metadata, and a featured-story blurb about dealership sales, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation with no substantive engineering narrative.</t>
+          <t>Body is mostly metadata and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Body is mostly a headline, date, and featured-story link with no substantive engineering narrative.</t>
+          <t>Body is mostly headline/date and a featured-story link, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Body is just a featured-story blurb and metadata, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story teaser and dealership list, with no substantive engineering or R&amp;D detail.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just metadata and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story teaser and dealership list, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2322,7 +2322,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Body is just a featured-story blurb and dealership sales teaser, with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly date stamps and featured-story links, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Body is just a brief retail legal note about a missing vehicle shipment, with no engineering or R&amp;D content.</t>
+          <t>Body is just a retail legal blurb about a missing vehicle shipment, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Body is just a timestamp and featured-story teaser, with no substantive engineering article content.</t>
+          <t>Body is a featured-story teaser with no substantive engineering article, so it offers no R&amp;D detail.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Body is just an opinion teaser and link about dealership group scale, with no engineering or R&amp;D content.</t>
+          <t>Body is just an opinion teaser and related list link about dealership group scale, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Body is just featured-story/navigation content with no substantive engineering article narrative.</t>
+          <t>Body is just featured-story/navigation text with no engineering article content.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Body is just a brief finance/legal teaser with no engineering or R&amp;D substance.</t>
+          <t>Body is just a brief lawsuit blurb and featured-story navigation with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Body is just a featured-story blurb and dates, with no substantive cybersecurity or engineering article content.</t>
+          <t>Body is mostly a featured-story teaser and sales list text, with no substantive engineering or cybersecurity article content.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and featured-story link about shipments, with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly dates and featured-story navigation with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -2650,7 +2650,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Body is just a featured-story/link stub with no engineering narrative or technical detail about the EV halt.</t>
+          <t>Body is mostly date blocks and a featured-story link, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -2691,7 +2691,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a dated featured-story blurb with no engineering narrative or technical substance.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Body is just a personnel move blurb with no engineering or R&amp;D substance.</t>
+          <t>Body is just a personnel listing with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a date, featured story teaser, and list-style promo with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Body is mostly a dated tariff-refund notice and featured-story promo, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a short tariff refund notice with featured story links, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -2921,7 +2921,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Body is just a newsletter/article list teaser with no engineering narrative, only a featured story link and sales/share mention.</t>
+          <t>Body is just a newsletter teaser and featured story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story promo and sales/listing teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured stories teaser and dealership list blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Body is just a podcast promo and dealership ranking teaser, with no substantive engineering or R&amp;D discussion.</t>
+          <t>Body is mostly a podcast/date blurb and dealership ranking teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Body is mostly a sponsored profile/metadata with no substantive automotive engineering content beyond a job title.</t>
+          <t>Body is a brief sponsor/profile intro with no engineering narrative or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Body is mostly dates and a featured-story link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly date and featured-story navigation with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories blurb and list-style promo, with no substantive engineering article narrative.</t>
+          <t>Body is just a featured-stories teaser and dealership list blurb, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Body is mostly date blocks and a featured story teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly dates and featured-story navigation, with no substantive engineering narrative relevant to automotive R&amp;D.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3217,7 +3217,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Body is mostly featured-story/navigation text with no substantive engineering narrative.</t>
+          <t>Body is mostly featured-story navigation and a sales blurb, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Body is a featured-story stub with a dealership-list teaser, not a substantive engineering article.</t>
+          <t>Body is just a featured-story teaser and dates, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Body is just a promotional landing page with no substantive engineering article or technical detail.</t>
+          <t>The body is essentially a promo/landing page with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Body is mostly timestamps and a featured-story list, with no substantive engineering article narrative.</t>
+          <t>Body is just update stamps and a featured-story link, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -3438,7 +3438,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Body is mostly byline, date, and featured-story/navigation text with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly author/date metadata and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Body is a featured-stories blurb with dealership-sales content, not substantive engineering detail about the EQS update.</t>
+          <t>Body is mostly dates and featured-story navigation, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Body is just a featured-story teaser and dealership list snippet, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly dates and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Body is a featured-story blurb and dealership list teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is a featured-story teaser about dealership sales, not an engineering article.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Body is just a brief legal/news stub about a dealership fraud case, with no automotive engineering or R&amp;D substance.</t>
+          <t>A dealership fraud appeal with no engineering or vehicle-development content in the article body.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured story/navigation text, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly date text and featured-story links, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Body is just a headline/date and a featured-stories link, with no engineering or R&amp;D narrative.</t>
+          <t>Body is just a headline/date and a featured-story link, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -3725,7 +3725,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Body is mostly timestamps and a featured-story blurb, with no substantive engineering narrative.</t>
+          <t>Body is mostly date/featured-story navigation with no substantive engineering narrative about the Juke EV.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories blurb with no technical article content or engineering detail.</t>
+          <t>Body is just a featured-story blurb and list-style metadata, with no substantive engineering article narrative.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -3807,7 +3807,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story link and a dealership-list blurb, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly dates and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3848,7 +3848,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Body is just a newsletter/event-style teaser and featured-story link, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a newsletter-style event mention and featured story blurb, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -3889,7 +3889,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Body is mostly navigation and a featured story blurb, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly dates and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story links, with no substantive engineering narrative about the Rogue or hybrid system.</t>
+          <t>Body is mostly a featured-story promo and dealership list metadata, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and date metadata, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story teaser with no engineering narrative; it’s a corporate investment and parts-hub announcement, not R&amp;D content.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Body is mostly metadata and a featured-story link, with no substantive engineering or R&amp;D article content.</t>
+          <t>Body is essentially a featured-story teaser/listing with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Body is just metadata and a featured story blurb, with no substantive engineering article content.</t>
+          <t>Body is just a featured-story teaser and sales blurb, with no substantive SDV engineering content.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Body is just a featured-story/link stub with sales-market copy, not an engineering or R&amp;D article.</t>
+          <t>Body is just a brief featured-story blurb and sales-list teaser, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and article list, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly metadata and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>A dealership-groups newsletter page with only a brief sales/share blurb and article links, not engineering or R&amp;D content.</t>
+          <t>Body is just a newsletter-style pointer to dealership rankings and sales/share growth, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and dealership ranking, with no substantive engineering narrative.</t>
+          <t>Body is mostly a featured-stories blurb and sales ranking teaser, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Body is just a dealership sale notice and featured-story link, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a dealership sale notice and teaser links, with no automotive engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Body is mostly metadata and a featured-stories link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly datestamps and a featured-story blurb, with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -4340,7 +4340,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Body is just a sales/featured-stories listing with no engineering or R&amp;D narrative.</t>
+          <t>Body is just a sales-data/listing page with dates and a featured story link, not an engineering article.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Body is mostly metadata and a featured-story link, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly timestamps and a featured-story link, with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>This is a LinkedIn sign-in page with no article narrative or engineering content.</t>
+          <t>Login/sign-in page with no article narrative or engineering content.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories promo and article metadata, with no substantive engineering narrative.</t>
+          <t>Body is mostly a featured-story teaser and dates, with no substantive automotive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -4504,7 +4504,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Body is just metadata and featured-story links about a tax case, with no engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story promo and dealership list teaser, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Body is mostly a headline and featured-story link about a dealership legal dispute, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a short retail/legal blurb with a featured-stories link, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -4586,7 +4586,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Body is just a sponsored landing/header with no technical article narrative; dealership workflow content is not automotive R&amp;D or engineering work.</t>
+          <t>Body is just a sponsored header/date with no engineering narrative, and the topic is dealership operations rather than automotive R&amp;D.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Body is just a date, featured story link, and a sales blurb with no engineering or R&amp;D substance.</t>
+          <t>Body is mostly timestamps and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Body is mostly navigation/featured-story text with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly dates and featured-story navigation with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly dates and featured-story/listing content, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Body is mostly metadata and a featured-story teaser, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly navigation/featured-story listing with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and dealership list blurb, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is a featured-story snippet and dealership-list teaser, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Body is just a featured-story teaser and dates with no engineering narrative or R&amp;D substance.</t>
+          <t>Body is just a featured-story teaser and dates, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and dealership-sales blurb, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story teaser and sales-list blurb, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Body is mostly date/footer and a featured-story list, with no substantive engineering narrative.</t>
+          <t>Body is mostly date blocks and featured-story navigation with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-story teaser and sales blurb, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a brief sales blurb with a featured-story link, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
@@ -4996,7 +4996,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>The body is mostly date stamps and featured-story navigation, with no substantive engineering or R&amp;D article narrative.</t>
+          <t>Body is mostly featured-story/navigation text with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>This is a dealership rankings/listing page with sales and revenue tables, not an engineering or R&amp;D article.</t>
+          <t>This is a dealership ranking/listing page dominated by sales and store-count tables, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>No article narrative is available; this is just a publication/access error page.</t>
+          <t>No article narrative is present; this is just an inaccessible issues page with a cookie notice.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Body is mostly date/featured-story navigation with no substantive engineering narrative; only approval headline context appears.</t>
+          <t>Body is mostly metadata and a featured-story link, with no substantive engineering or validation detail.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Body is just a rankings teaser and sales-summary blurb, with no engineering or R&amp;D substance.</t>
+          <t>Body is just a brief dealership ranking teaser with sales/share data, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Body is mostly a featured-stories teaser with sales-list context, not a substantive engineering article.</t>
+          <t>Body is mostly an article teaser and unrelated dealership sales blurbs, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -5242,7 +5242,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>This is a dealership ranking/listing page with only sales-share summary, not an engineering or R&amp;D article.</t>
+          <t>This is a dealership sales ranking/list page with no substantive engineering or R&amp;D content in the body.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -5283,7 +5283,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Body is just a short retail metric teaser with no engineering or R&amp;D substance.</t>
+          <t>This is a dealership performance blurb with no substantive engineering or R&amp;D content in the body.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Body is a dealership-sales summary with no engineering, R&amp;D, or technical substance.</t>
+          <t>Article is a dealership sales summary with no engineering, R&amp;D, or vehicle development content.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -5374,7 +5374,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Body is just a dealership rankings teaser with sales/share notes, not engineering or R&amp;D content.</t>
+          <t>Body is just a dealership list headline with sales/share summary, not engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Body is just a navigation skip line with no article narrative or engineering content.</t>
+          <t>Body is just a navigation skip line from a dealership ranking page, with no technical article content.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Body is mostly podcast/listing and dealership teaser content, with no substantive engineering or R&amp;D discussion.</t>
+          <t>Body is mostly a featured-story/listing page with no substantive engineering article content.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
@@ -5563,7 +5563,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>This is a classifieds/listing page with only navigation and teaser content, not an engineering article.</t>
+          <t>This is a classifieds/topic landing page with only navigation and a featured-story blurb, not a substantive engineering article.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>This is a sales-data listing page with no substantive engineering or R&amp;D article narrative.</t>
+          <t>Body is just a sales-data listing and featured-story teaser, with no engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Body is just a brief Top 150 teaser with navigation and sales-share note, not substantive engineering content.</t>
+          <t>Body is a short rankings teaser with no engineering narrative; it mainly references dealership list trends and metadata.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Body is just a brief downtime/listing page with no engineering narrative or technical detail.</t>
+          <t>Body is mostly a featured-story teaser and date metadata, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Body is just a newsletter-style teaser and dealer advertising compliance link, with no substantive automotive engineering or R&amp;D content.</t>
+          <t>Body is just a newsletter teaser and article list item about dealer advertising, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Body is just a featured-stories/listing page with dealership sales snippets, not substantive engineering content.</t>
+          <t>Body is just a featured stories/listing page with dealership sales recap, not substantive automotive engineering content.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Body is just a featured-story teaser and metadata, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly metadata and a featured-story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Body is mostly metadata and unrelated featured-story teasers, with no engineering or R&amp;D substance.</t>
+          <t>Body is essentially a brief/news stub about street naming and featured links, with no engineering or R&amp;D substance.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Body is just a featured-story teaser and sales list snippet, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a featured-story teaser and sales-list blurb, with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Body is a webinar/news blurb with no engineering or R&amp;D substance, only dealership advertising compliance and teaser links.</t>
+          <t>Body is mostly featured-story/listing text about dealership advertising compliance, with no substantive automotive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Body is mostly a headline and featured-story link, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly a headline/date and featured story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>This is mostly a customer incentives/listing page with featured-story links and no substantive engineering or R&amp;D content.</t>
+          <t>Body is a sales/incentives listing with featured story teaser, not substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Body is mostly date blocks and featured-story navigation, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is just a featured-story teaser and dates, with no substantive engineering or R&amp;D article content.</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Body is mostly featured-story/listing text with no substantive engineering article about Magna’s divestment.</t>
+          <t>Body is just metadata and a featured story link, with no substantive engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Body is mostly dateline and featured-story navigation, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is just a date and featured-story teaser, with no substantive engineering or R&amp;D article content.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Body is just a brief dealership buy-sell/news teaser with a linked feature, not engineering or R&amp;D content.</t>
+          <t>Body is just a short business blurb and featured-story link about dealership acquisitions, with no engineering or R&amp;D content.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Body is mostly dates and featured-story navigation, with no substantive engineering or R&amp;D narrative.</t>
+          <t>Body is mostly dates and featured-story navigation with no substantive engineering or R&amp;D narrative.</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Body is just a featured-story blurb and list-style metadata, with no substantive engineering or R&amp;D content.</t>
+          <t>Body is mostly a featured-story/listing blurb with no substantive engineering narrative.</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Body is just a headline and featured-story promo, with no substantive engineering or battery-development detail.</t>
+          <t>Body is just a headline, date, and teaser link with no substantive engineering article.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -6383,7 +6383,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Body is just a podcast teaser and link list with dealership sales context, not engineering or R&amp;D content.</t>
+          <t>Mostly a podcast promo and retail/business teaser with no substantive engineering or R&amp;D content in the body.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
